--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0066.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0066.xlsx
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Thôi đi! Bộ bài của ta đủ mạnh rồi! Cứ tấn công đi!</t>
+          <t>Thôi đi! Bộ bài của tao đủ mạnh rồi! Cứ tấn công đi!</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Anh ta đây rồi! Ta thấy rồi! Cuối cùng cũng chịu xuất hiện!</t>
+          <t>Anh ta đây rồi! Tao thấy rồi! Cuối cùng cũng chịu xuất hiện!</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chuyện đó để sau! Trước tiên, xem chiến thuật mới của ta hiệu quả thế nào đã!</t>
+          <t>Chuyện đó để sau! Trước tiên, xem chiến thuật mới của tao hiệu quả thế nào đã!</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Nghĩa là danh sách những kẻ ta phải trả thù giờ là... một, hai... hai mươi sáu... bảy mươi tám...</t>
+          <t>Nghĩa là danh sách những kẻ tao phải trả thù giờ là... một, hai... hai mươi sáu... bảy mươi tám...</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Ta sẽ đánh bại ngươi...</t>
+          <t>Tao sẽ đánh bại ngươi...</t>
         </is>
       </c>
     </row>
